--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
@@ -1842,12 +1847,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -12307,7 +12312,7 @@
         <v>100</v>
       </c>
       <c r="F6" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -12379,7 +12384,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -12415,7 +12420,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -12451,7 +12456,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -12487,7 +12492,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -12523,7 +12528,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -12559,7 +12564,7 @@
         <v>100</v>
       </c>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -12595,7 +12600,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -12631,7 +12636,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -12667,7 +12672,7 @@
         <v>100</v>
       </c>
       <c r="F16" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -12703,7 +12708,7 @@
         <v>100</v>
       </c>
       <c r="F17" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -12750,7 +12755,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -12786,7 +12791,7 @@
         <v>20</v>
       </c>
       <c r="F20" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -12826,7 +12831,7 @@
         <v>20</v>
       </c>
       <c r="F21" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -12862,7 +12867,7 @@
         <v>20</v>
       </c>
       <c r="F22" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -12913,7 +12918,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G25" s="1">
         <v>2</v>
@@ -12982,7 +12987,7 @@
         <v>100</v>
       </c>
       <c r="F27" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G27" s="1">
         <v>2</v>
@@ -13018,7 +13023,7 @@
         <v>100</v>
       </c>
       <c r="F28" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G28" s="1">
         <v>2</v>
@@ -13054,7 +13059,7 @@
         <v>100</v>
       </c>
       <c r="F29" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G29" s="1">
         <v>2</v>
@@ -13090,7 +13095,7 @@
         <v>100</v>
       </c>
       <c r="F30" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G30" s="1">
         <v>2</v>
@@ -13126,7 +13131,7 @@
         <v>100</v>
       </c>
       <c r="F31" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
@@ -13162,7 +13167,7 @@
         <v>100</v>
       </c>
       <c r="F32" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -13198,7 +13203,7 @@
         <v>100</v>
       </c>
       <c r="F33" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -13234,7 +13239,7 @@
         <v>100</v>
       </c>
       <c r="F34" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
         <v>2</v>
@@ -13270,7 +13275,7 @@
         <v>100</v>
       </c>
       <c r="F35" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
@@ -13306,7 +13311,7 @@
         <v>100</v>
       </c>
       <c r="F36" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
@@ -13347,7 +13352,7 @@
         <v>20</v>
       </c>
       <c r="F38" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
@@ -13380,7 +13385,7 @@
         <v>20</v>
       </c>
       <c r="F39" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
@@ -13419,7 +13424,7 @@
         <v>20</v>
       </c>
       <c r="F40" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -13459,7 +13464,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1">
         <v>2</v>
@@ -13529,7 +13534,7 @@
         <v>100</v>
       </c>
       <c r="F45" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G45" s="1">
         <v>3</v>
@@ -13601,7 +13606,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G47" s="1">
         <v>3</v>
@@ -13637,7 +13642,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G48" s="1">
         <v>3</v>
@@ -13673,7 +13678,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -13709,7 +13714,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G50" s="1">
         <v>3</v>
@@ -13745,7 +13750,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -13781,7 +13786,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G52" s="1">
         <v>3</v>
@@ -13817,7 +13822,7 @@
         <v>100</v>
       </c>
       <c r="F53" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G53" s="1">
         <v>3</v>
@@ -13853,7 +13858,7 @@
         <v>100</v>
       </c>
       <c r="F54" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G54" s="1">
         <v>3</v>
@@ -13889,7 +13894,7 @@
         <v>100</v>
       </c>
       <c r="F55" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G55" s="1">
         <v>3</v>
@@ -13922,7 +13927,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G56" s="1">
         <v>3</v>
@@ -13982,7 +13987,7 @@
         <v>20</v>
       </c>
       <c r="F59" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G59" s="1">
         <v>3</v>
@@ -14015,7 +14020,7 @@
         <v>20</v>
       </c>
       <c r="F60" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G60" s="1">
         <v>3</v>
@@ -14052,7 +14057,7 @@
         <v>20</v>
       </c>
       <c r="F61" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G61" s="1">
         <v>3</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="批量配置" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="暗金" sheetId="4" r:id="rId4"/>
     <sheet name="混沌" sheetId="5" r:id="rId5"/>
     <sheet name="虚无" sheetId="6" r:id="rId6"/>
+    <sheet name="寂灭" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -558,8 +559,86 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击力系数（百分比），额外附加固定伤害值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 以自己为圆心
+1 距离1格</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="413">
   <si>
     <t>_ID</t>
   </si>
@@ -1663,6 +1742,141 @@
   </si>
   <si>
     <t>召唤白虎·复制Ⅱ</t>
+  </si>
+  <si>
+    <t>基础剑术·超脱</t>
+  </si>
+  <si>
+    <t>提高此技能系数120%系数增幅</t>
+  </si>
+  <si>
+    <t>流光剑法·超脱</t>
+  </si>
+  <si>
+    <t>旋风斩·超脱</t>
+  </si>
+  <si>
+    <t>腾空斩·超脱</t>
+  </si>
+  <si>
+    <t>武神盾·超脱</t>
+  </si>
+  <si>
+    <t>武力精通·超脱</t>
+  </si>
+  <si>
+    <t>烈焰斩·超脱</t>
+  </si>
+  <si>
+    <t>战吼·超脱</t>
+  </si>
+  <si>
+    <t>裂天斩·超脱</t>
+  </si>
+  <si>
+    <t>裂地斩·超脱</t>
+  </si>
+  <si>
+    <t>战士之魂·超脱</t>
+  </si>
+  <si>
+    <t>剑二十三·超脱</t>
+  </si>
+  <si>
+    <t>提高此技能系数80%系数增幅</t>
+  </si>
+  <si>
+    <t>此技能额外增加80%命中</t>
+  </si>
+  <si>
+    <t>战吼·破限Ⅲ</t>
+  </si>
+  <si>
+    <t>火球术·超脱</t>
+  </si>
+  <si>
+    <t>落雷术·超脱</t>
+  </si>
+  <si>
+    <t>火焰墙·超脱</t>
+  </si>
+  <si>
+    <t>烈焰环·超脱</t>
+  </si>
+  <si>
+    <t>法力盾·超脱</t>
+  </si>
+  <si>
+    <t>法术精通·超脱</t>
+  </si>
+  <si>
+    <t>冰爆术·超脱</t>
+  </si>
+  <si>
+    <t>心灵传送·超脱</t>
+  </si>
+  <si>
+    <t>毁灭流星·超脱</t>
+  </si>
+  <si>
+    <t>分身术·超脱</t>
+  </si>
+  <si>
+    <t>法师之魂·超脱</t>
+  </si>
+  <si>
+    <t>魔尊附体·超脱</t>
+  </si>
+  <si>
+    <t>冰爆术·哀霜Ⅳ</t>
+  </si>
+  <si>
+    <t>使敌人受到的伤害增加50%，持续5秒</t>
+  </si>
+  <si>
+    <t>心灵传送·破限Ⅲ</t>
+  </si>
+  <si>
+    <t>魔尊附体·双倍Ⅲ</t>
+  </si>
+  <si>
+    <t>疗伤术·超脱</t>
+  </si>
+  <si>
+    <t>驱魔符·超脱</t>
+  </si>
+  <si>
+    <t>毒咒术·超脱</t>
+  </si>
+  <si>
+    <t>召唤小兵·超脱</t>
+  </si>
+  <si>
+    <t>道力盾·超脱</t>
+  </si>
+  <si>
+    <t>道力精通·超脱</t>
+  </si>
+  <si>
+    <t>召唤魔兽·超脱</t>
+  </si>
+  <si>
+    <t>隐身道法·超脱</t>
+  </si>
+  <si>
+    <t>召唤月神·超脱</t>
+  </si>
+  <si>
+    <t>无极道体·超脱</t>
+  </si>
+  <si>
+    <t>道士之魂·超脱</t>
+  </si>
+  <si>
+    <t>召唤白虎·超脱</t>
+  </si>
+  <si>
+    <t>隐身道法·破限Ⅲ</t>
   </si>
 </sst>
 </file>
@@ -14088,4 +14302,1828 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:U61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="15.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C6" s="1">
+        <v>51001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1">
+        <v>100</v>
+      </c>
+      <c r="F6" s="1">
+        <v>500</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L6" s="1">
+        <v>120</v>
+      </c>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C7" s="1">
+        <v>51002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1">
+        <v>100</v>
+      </c>
+      <c r="F7" s="1">
+        <v>100</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1002</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L7" s="1">
+        <v>120</v>
+      </c>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C8" s="1">
+        <v>51003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1">
+        <v>500</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1003</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L8" s="1">
+        <v>120</v>
+      </c>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C9" s="1">
+        <v>51004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100</v>
+      </c>
+      <c r="F9" s="1">
+        <v>500</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1004</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L9" s="1">
+        <v>120</v>
+      </c>
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C10" s="1">
+        <v>51005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1005</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L10" s="1">
+        <v>120</v>
+      </c>
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C11" s="1">
+        <v>51006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+      <c r="F11" s="1">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1006</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L11" s="1">
+        <v>120</v>
+      </c>
+      <c r="P11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C12" s="1">
+        <v>51007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1">
+        <v>100</v>
+      </c>
+      <c r="F12" s="1">
+        <v>500</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1007</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L12" s="1">
+        <v>120</v>
+      </c>
+      <c r="P12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C13" s="1">
+        <v>51008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1">
+        <v>100</v>
+      </c>
+      <c r="F13" s="1">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L13" s="1">
+        <v>120</v>
+      </c>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C14" s="1">
+        <v>51009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1">
+        <v>100</v>
+      </c>
+      <c r="F14" s="1">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1009</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L14" s="1">
+        <v>120</v>
+      </c>
+      <c r="P14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C15" s="1">
+        <v>51010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>100</v>
+      </c>
+      <c r="F15" s="1">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1010</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L15" s="1">
+        <v>120</v>
+      </c>
+      <c r="P15" s="4"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C16" s="1">
+        <v>51011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1">
+        <v>100</v>
+      </c>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1011</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L16" s="1">
+        <v>120</v>
+      </c>
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C17" s="1">
+        <v>51012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1">
+        <v>100</v>
+      </c>
+      <c r="F17" s="1">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1012</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="L17" s="1">
+        <v>80</v>
+      </c>
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="H18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="4"/>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C19" s="1">
+        <v>51102</v>
+      </c>
+      <c r="D19" s="1">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1">
+        <v>20</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1002</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="O19" s="4"/>
+      <c r="P19" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C20" s="1">
+        <v>51108</v>
+      </c>
+      <c r="D20" s="1">
+        <v>7</v>
+      </c>
+      <c r="E20" s="1">
+        <v>20</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1008</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O20" s="4"/>
+      <c r="R20" s="1">
+        <v>3</v>
+      </c>
+      <c r="U20" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C21" s="1">
+        <v>51110</v>
+      </c>
+      <c r="D21" s="1">
+        <v>7</v>
+      </c>
+      <c r="E21" s="1">
+        <v>20</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1010</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="O21" s="4"/>
+      <c r="P21" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C22" s="1">
+        <v>51112</v>
+      </c>
+      <c r="D22" s="1">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1">
+        <v>20</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1012</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="O22" s="4"/>
+      <c r="P22" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:21">
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="3:21">
+      <c r="H24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C25" s="1">
+        <v>52001</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7</v>
+      </c>
+      <c r="E25" s="1">
+        <v>100</v>
+      </c>
+      <c r="F25" s="1">
+        <v>500</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2001</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L25" s="1">
+        <v>120</v>
+      </c>
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C26" s="1">
+        <v>52002</v>
+      </c>
+      <c r="D26" s="1">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1">
+        <v>100</v>
+      </c>
+      <c r="F26" s="1">
+        <v>100</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2002</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L26" s="1">
+        <v>120</v>
+      </c>
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C27" s="1">
+        <v>52003</v>
+      </c>
+      <c r="D27" s="1">
+        <v>7</v>
+      </c>
+      <c r="E27" s="1">
+        <v>100</v>
+      </c>
+      <c r="F27" s="1">
+        <v>500</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2003</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L27" s="1">
+        <v>120</v>
+      </c>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C28" s="1">
+        <v>52004</v>
+      </c>
+      <c r="D28" s="1">
+        <v>7</v>
+      </c>
+      <c r="E28" s="1">
+        <v>100</v>
+      </c>
+      <c r="F28" s="1">
+        <v>500</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2004</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L28" s="1">
+        <v>120</v>
+      </c>
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C29" s="1">
+        <v>52005</v>
+      </c>
+      <c r="D29" s="1">
+        <v>7</v>
+      </c>
+      <c r="E29" s="1">
+        <v>100</v>
+      </c>
+      <c r="F29" s="1">
+        <v>50</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2005</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L29" s="1">
+        <v>120</v>
+      </c>
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C30" s="1">
+        <v>52006</v>
+      </c>
+      <c r="D30" s="1">
+        <v>7</v>
+      </c>
+      <c r="E30" s="1">
+        <v>100</v>
+      </c>
+      <c r="F30" s="1">
+        <v>50</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2006</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L30" s="1">
+        <v>120</v>
+      </c>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C31" s="1">
+        <v>52007</v>
+      </c>
+      <c r="D31" s="1">
+        <v>7</v>
+      </c>
+      <c r="E31" s="1">
+        <v>100</v>
+      </c>
+      <c r="F31" s="1">
+        <v>500</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2007</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L31" s="1">
+        <v>120</v>
+      </c>
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C32" s="1">
+        <v>52008</v>
+      </c>
+      <c r="D32" s="1">
+        <v>7</v>
+      </c>
+      <c r="E32" s="1">
+        <v>100</v>
+      </c>
+      <c r="F32" s="1">
+        <v>20</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2008</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L32" s="1">
+        <v>120</v>
+      </c>
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C33" s="1">
+        <v>52009</v>
+      </c>
+      <c r="D33" s="1">
+        <v>7</v>
+      </c>
+      <c r="E33" s="1">
+        <v>100</v>
+      </c>
+      <c r="F33" s="1">
+        <v>30</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2009</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L33" s="1">
+        <v>120</v>
+      </c>
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C34" s="1">
+        <v>52010</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1">
+        <v>100</v>
+      </c>
+      <c r="F34" s="1">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>2010</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L34" s="1">
+        <v>120</v>
+      </c>
+      <c r="P34" s="4"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C35" s="1">
+        <v>52011</v>
+      </c>
+      <c r="D35" s="1">
+        <v>7</v>
+      </c>
+      <c r="E35" s="1">
+        <v>100</v>
+      </c>
+      <c r="F35" s="1">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2011</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L35" s="1">
+        <v>120</v>
+      </c>
+      <c r="P35" s="4"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C36" s="1">
+        <v>52012</v>
+      </c>
+      <c r="D36" s="1">
+        <v>7</v>
+      </c>
+      <c r="E36" s="1">
+        <v>100</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>2012</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="L36" s="1">
+        <v>80</v>
+      </c>
+      <c r="P36" s="4"/>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:21">
+      <c r="H37" s="3"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C38" s="1">
+        <v>52102</v>
+      </c>
+      <c r="D38" s="1">
+        <v>7</v>
+      </c>
+      <c r="E38" s="1">
+        <v>20</v>
+      </c>
+      <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="3">
+        <v>2002</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="O38" s="4"/>
+      <c r="P38" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C39" s="1">
+        <v>52107</v>
+      </c>
+      <c r="D39" s="1">
+        <v>7</v>
+      </c>
+      <c r="E39" s="1">
+        <v>20</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2007</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="O39" s="1">
+        <v>50</v>
+      </c>
+      <c r="P39" s="4"/>
+      <c r="U39" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C40" s="1">
+        <v>52108</v>
+      </c>
+      <c r="D40" s="1">
+        <v>7</v>
+      </c>
+      <c r="E40" s="1">
+        <v>20</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+      <c r="H40" s="3">
+        <v>2008</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O40" s="4"/>
+      <c r="Q40" s="1"/>
+      <c r="R40">
+        <v>3</v>
+      </c>
+      <c r="U40" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C41" s="1">
+        <v>52112</v>
+      </c>
+      <c r="D41" s="1">
+        <v>7</v>
+      </c>
+      <c r="E41" s="1">
+        <v>20</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2012</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="P41" s="4"/>
+      <c r="R41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="4"/>
+      <c r="U42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="1"/>
+      <c r="P43" s="4"/>
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:21">
+      <c r="H44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="4"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C45" s="1">
+        <v>53001</v>
+      </c>
+      <c r="D45" s="1">
+        <v>7</v>
+      </c>
+      <c r="E45" s="1">
+        <v>100</v>
+      </c>
+      <c r="F45" s="1">
+        <v>500</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3001</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L45" s="1">
+        <v>120</v>
+      </c>
+      <c r="P45" s="4"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C46" s="1">
+        <v>53002</v>
+      </c>
+      <c r="D46" s="1">
+        <v>7</v>
+      </c>
+      <c r="E46" s="1">
+        <v>100</v>
+      </c>
+      <c r="F46" s="1">
+        <v>100</v>
+      </c>
+      <c r="G46" s="1">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
+        <v>3002</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L46" s="1">
+        <v>120</v>
+      </c>
+      <c r="P46" s="4"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C47" s="1">
+        <v>53003</v>
+      </c>
+      <c r="D47" s="1">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>100</v>
+      </c>
+      <c r="F47" s="1">
+        <v>500</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
+        <v>3003</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L47" s="1">
+        <v>120</v>
+      </c>
+      <c r="P47" s="4"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C48" s="1">
+        <v>53004</v>
+      </c>
+      <c r="D48" s="1">
+        <v>7</v>
+      </c>
+      <c r="E48" s="1">
+        <v>100</v>
+      </c>
+      <c r="F48" s="1">
+        <v>500</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
+        <v>3004</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L48" s="1">
+        <v>120</v>
+      </c>
+      <c r="P48" s="4"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C49" s="1">
+        <v>53005</v>
+      </c>
+      <c r="D49" s="1">
+        <v>7</v>
+      </c>
+      <c r="E49" s="1">
+        <v>100</v>
+      </c>
+      <c r="F49" s="1">
+        <v>50</v>
+      </c>
+      <c r="G49" s="1">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3">
+        <v>3005</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L49" s="1">
+        <v>120</v>
+      </c>
+      <c r="P49" s="4"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C50" s="1">
+        <v>53006</v>
+      </c>
+      <c r="D50" s="1">
+        <v>7</v>
+      </c>
+      <c r="E50" s="1">
+        <v>100</v>
+      </c>
+      <c r="F50" s="1">
+        <v>50</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3</v>
+      </c>
+      <c r="H50" s="3">
+        <v>3006</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L50" s="1">
+        <v>120</v>
+      </c>
+      <c r="P50" s="4"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C51" s="1">
+        <v>53007</v>
+      </c>
+      <c r="D51" s="1">
+        <v>7</v>
+      </c>
+      <c r="E51" s="1">
+        <v>100</v>
+      </c>
+      <c r="F51" s="1">
+        <v>500</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
+      <c r="H51" s="3">
+        <v>3007</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L51" s="1">
+        <v>120</v>
+      </c>
+      <c r="P51" s="4"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C52" s="1">
+        <v>53008</v>
+      </c>
+      <c r="D52" s="1">
+        <v>7</v>
+      </c>
+      <c r="E52" s="1">
+        <v>100</v>
+      </c>
+      <c r="F52" s="1">
+        <v>20</v>
+      </c>
+      <c r="G52" s="1">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3008</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L52" s="1">
+        <v>120</v>
+      </c>
+      <c r="P52" s="4"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C53" s="1">
+        <v>53009</v>
+      </c>
+      <c r="D53" s="1">
+        <v>7</v>
+      </c>
+      <c r="E53" s="1">
+        <v>100</v>
+      </c>
+      <c r="F53" s="1">
+        <v>30</v>
+      </c>
+      <c r="G53" s="1">
+        <v>3</v>
+      </c>
+      <c r="H53" s="3">
+        <v>3009</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L53" s="1">
+        <v>120</v>
+      </c>
+      <c r="P53" s="4"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C54" s="1">
+        <v>53010</v>
+      </c>
+      <c r="D54" s="1">
+        <v>7</v>
+      </c>
+      <c r="E54" s="1">
+        <v>100</v>
+      </c>
+      <c r="F54" s="1">
+        <v>10</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
+        <v>3010</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L54" s="1">
+        <v>120</v>
+      </c>
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C55" s="1">
+        <v>53011</v>
+      </c>
+      <c r="D55" s="1">
+        <v>7</v>
+      </c>
+      <c r="E55" s="1">
+        <v>100</v>
+      </c>
+      <c r="F55" s="1">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1">
+        <v>3</v>
+      </c>
+      <c r="H55" s="3">
+        <v>3011</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L55" s="1">
+        <v>120</v>
+      </c>
+      <c r="P55" s="4"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C56" s="1">
+        <v>53012</v>
+      </c>
+      <c r="D56" s="1">
+        <v>7</v>
+      </c>
+      <c r="E56" s="1">
+        <v>100</v>
+      </c>
+      <c r="F56" s="1">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3</v>
+      </c>
+      <c r="H56" s="3">
+        <v>3012</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="L56" s="1">
+        <v>80</v>
+      </c>
+      <c r="P56" s="4"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="U57" s="1"/>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="H58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="4"/>
+      <c r="P58" s="4"/>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C59" s="1">
+        <v>53102</v>
+      </c>
+      <c r="D59" s="1">
+        <v>7</v>
+      </c>
+      <c r="E59" s="1">
+        <v>20</v>
+      </c>
+      <c r="F59" s="1">
+        <v>5</v>
+      </c>
+      <c r="G59" s="1">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3002</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="O59" s="4"/>
+      <c r="P59" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C60" s="1">
+        <v>53208</v>
+      </c>
+      <c r="D60" s="1">
+        <v>7</v>
+      </c>
+      <c r="E60" s="1">
+        <v>20</v>
+      </c>
+      <c r="F60" s="1">
+        <v>5</v>
+      </c>
+      <c r="G60" s="1">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
+        <v>3008</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O60" s="4"/>
+      <c r="Q60" s="1"/>
+      <c r="R60">
+        <v>3</v>
+      </c>
+      <c r="U60" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:21">
+      <c r="H61" s="3"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="S3:S5 C3:L5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>